--- a/data/Diessenhofen/investment_decision/Diessenhofen_SFH_from_2015_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Diessenhofen_SFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>117.3856160060552</v>
+        <v>136.8791093126116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>21821.19668633676</v>
       </c>
       <c r="F4" t="n">
-        <v>118.1565936</v>
+        <v>127.8559334880155</v>
       </c>
       <c r="G4" t="n">
         <v>21821.19668633676</v>
       </c>
       <c r="H4" t="n">
-        <v>118.2973154929809</v>
+        <v>137.6031322664288</v>
       </c>
       <c r="I4" t="n">
         <v>21821.19668633676</v>
       </c>
       <c r="J4" t="n">
-        <v>118.2973154929809</v>
+        <v>124.3545905648974</v>
       </c>
       <c r="K4" t="n">
         <v>21821.19668633676</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>131.557781553127</v>
+        <v>155.2361151439459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>21821.19668633676</v>
       </c>
       <c r="F5" t="n">
-        <v>131.557781553127</v>
+        <v>149.2204201049363</v>
       </c>
       <c r="G5" t="n">
         <v>21821.19668633676</v>
       </c>
       <c r="H5" t="n">
-        <v>131.667196590516</v>
+        <v>156.0673712372657</v>
       </c>
       <c r="I5" t="n">
         <v>21821.19668633676</v>
       </c>
       <c r="J5" t="n">
-        <v>131.667196590516</v>
+        <v>150.5649176707009</v>
       </c>
       <c r="K5" t="n">
         <v>21821.19668633676</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>131.557781553127</v>
+        <v>155.2361151439459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>21821.19668633676</v>
       </c>
       <c r="F6" t="n">
-        <v>131.5577815531269</v>
+        <v>149.2204201049363</v>
       </c>
       <c r="G6" t="n">
         <v>21821.19668633676</v>
       </c>
       <c r="H6" t="n">
-        <v>131.667196590516</v>
+        <v>156.0673712372657</v>
       </c>
       <c r="I6" t="n">
         <v>21821.19668633676</v>
       </c>
       <c r="J6" t="n">
-        <v>131.667196590516</v>
+        <v>150.5649176707009</v>
       </c>
       <c r="K6" t="n">
         <v>21821.19668633676</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>32.73179502950514</v>
+        <v>52.9116808988764</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009065723294117648</v>
+        <v>0.005892720141176471</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.009065723294117648</v>
+        <v>0.005892720141176471</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.009065723294117648</v>
+        <v>0.006346006305882353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009065723294117648</v>
+        <v>0.006346006305882353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00906572329411765</v>
+        <v>0.005892720141176471</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00906572329411765</v>
+        <v>0.005892720141176471</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00951900945882353</v>
+        <v>0.006346006305882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00951900945882353</v>
+        <v>0.006346006305882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.00906572329411765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.009065723294117648</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.00906572329411765</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.009270856354986404</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.00906572329411765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.00906572329411765</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01087886795294118</v>
+        <v>0.00906572329411765</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01087886795294118</v>
+        <v>0.009270856354986404</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.009065723294117648</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0104255817882353</v>
+        <v>0.00906572329411765</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01087886795294118</v>
+        <v>0.009065723294117648</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01087886795294118</v>
+        <v>0.009270856354986404</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>1.335070988491559</v>
+        <v>0.5963943442948229</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>8.09115804</v>
       </c>
       <c r="F20" t="n">
-        <v>1.335070988491559</v>
+        <v>0.6519338327409181</v>
       </c>
       <c r="G20" t="n">
         <v>8.09115804</v>
       </c>
       <c r="H20" t="n">
-        <v>1.335070988491559</v>
+        <v>0.4778256144765149</v>
       </c>
       <c r="I20" t="n">
         <v>8.09115804</v>
       </c>
       <c r="J20" t="n">
-        <v>1.335070988491559</v>
+        <v>0.4783381978189565</v>
       </c>
       <c r="K20" t="n">
         <v>8.09115804</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>1.335070988491559</v>
+        <v>0.7063678860411058</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>8.09115804</v>
       </c>
       <c r="F21" t="n">
-        <v>1.335070988491559</v>
+        <v>0.692625533819861</v>
       </c>
       <c r="G21" t="n">
         <v>8.09115804</v>
       </c>
       <c r="H21" t="n">
-        <v>1.335070988491559</v>
+        <v>0.5193261880455841</v>
       </c>
       <c r="I21" t="n">
         <v>8.09115804</v>
       </c>
       <c r="J21" t="n">
-        <v>1.335070988491559</v>
+        <v>0.5447686582375149</v>
       </c>
       <c r="K21" t="n">
         <v>8.09115804</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1.185598343241431</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>8.09115804</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.204041374999999</v>
       </c>
       <c r="G30" t="n">
         <v>8.09115804</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.249320515030472</v>
       </c>
       <c r="I30" t="n">
         <v>8.09115804</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.314728123277731</v>
       </c>
       <c r="K30" t="n">
         <v>8.09115804</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.259201647555678</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>8.09115804</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.330710151841368</v>
       </c>
       <c r="G31" t="n">
         <v>8.09115804</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.428742781448053</v>
       </c>
       <c r="I31" t="n">
         <v>8.09115804</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.460862729231435</v>
       </c>
       <c r="K31" t="n">
         <v>8.09115804</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>3.778547167495091</v>
+        <v>4.069278972123219</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>41.44376317104298</v>
       </c>
       <c r="F54" t="n">
-        <v>3.627200608192093</v>
+        <v>3.773348749811735</v>
       </c>
       <c r="G54" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="H54" t="n">
-        <v>3.626256924417797</v>
+        <v>4.06342889112205</v>
       </c>
       <c r="I54" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="J54" t="n">
-        <v>3.758436149401142</v>
+        <v>3.773348749811735</v>
       </c>
       <c r="K54" t="n">
         <v>41.44376317104298</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>6.465925868662625</v>
+        <v>6.716377320267271</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>41.44376317104298</v>
       </c>
       <c r="F55" t="n">
-        <v>6.002795250474271</v>
+        <v>6.315295630347798</v>
       </c>
       <c r="G55" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="H55" t="n">
-        <v>5.948005924243041</v>
+        <v>6.712684446130969</v>
       </c>
       <c r="I55" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="J55" t="n">
-        <v>6.392679274687977</v>
+        <v>6.211390625868419</v>
       </c>
       <c r="K55" t="n">
         <v>41.44376317104298</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>6.465925868662625</v>
+        <v>6.716377320267271</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>41.44376317104298</v>
       </c>
       <c r="F56" t="n">
-        <v>6.002795250474271</v>
+        <v>6.315295630347798</v>
       </c>
       <c r="G56" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="H56" t="n">
-        <v>5.948005924243041</v>
+        <v>6.71268444613097</v>
       </c>
       <c r="I56" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="J56" t="n">
-        <v>6.392679274687977</v>
+        <v>6.211390625868419</v>
       </c>
       <c r="K56" t="n">
         <v>41.44376317104298</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>6.452669527675164</v>
+        <v>1.748400882358817</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>41.44376317104298</v>
       </c>
       <c r="F64" t="n">
-        <v>6.587009228288203</v>
+        <v>2.25787216700616</v>
       </c>
       <c r="G64" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="H64" t="n">
-        <v>6.584848752658508</v>
+        <v>1.737116349813808</v>
       </c>
       <c r="I64" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="J64" t="n">
-        <v>6.452669527675162</v>
+        <v>2.325313121864835</v>
       </c>
       <c r="K64" t="n">
         <v>41.44376317104298</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>6.452669527675164</v>
+        <v>1.748400882358817</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>41.44376317104298</v>
       </c>
       <c r="F65" t="n">
-        <v>6.915800145863519</v>
+        <v>2.25787216700616</v>
       </c>
       <c r="G65" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="H65" t="n">
-        <v>6.968175905093521</v>
+        <v>1.737116349813808</v>
       </c>
       <c r="I65" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="J65" t="n">
-        <v>6.523502554648584</v>
+        <v>2.325313121864835</v>
       </c>
       <c r="K65" t="n">
         <v>41.44376317104298</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>6.452669527675164</v>
+        <v>1.748400882358817</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>41.44376317104298</v>
       </c>
       <c r="F66" t="n">
-        <v>6.915800145863519</v>
+        <v>2.25787216700616</v>
       </c>
       <c r="G66" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="H66" t="n">
-        <v>6.968175905093521</v>
+        <v>1.737116349813808</v>
       </c>
       <c r="I66" t="n">
         <v>41.44376317104298</v>
       </c>
       <c r="J66" t="n">
-        <v>6.523502554648584</v>
+        <v>2.325313121864835</v>
       </c>
       <c r="K66" t="n">
         <v>41.44376317104298</v>
